--- a/artfynd/A 38086-2024 artfynd.xlsx
+++ b/artfynd/A 38086-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114571334</v>
+        <v>114571331</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581410</v>
+        <v>581564</v>
       </c>
       <c r="R2" t="n">
-        <v>6764652</v>
+        <v>6764637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,40 +776,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114571332</v>
+        <v>114571337</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581642</v>
+        <v>581405</v>
       </c>
       <c r="R3" t="n">
-        <v>6764710</v>
+        <v>6764646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114571331</v>
+        <v>114571332</v>
       </c>
       <c r="B4" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581564</v>
+        <v>581642</v>
       </c>
       <c r="R4" t="n">
-        <v>6764637</v>
+        <v>6764710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,15 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114571337</v>
+        <v>114571333</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,28 +993,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1044,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581405</v>
+        <v>581542</v>
       </c>
       <c r="R5" t="n">
-        <v>6764646</v>
+        <v>6764691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114571333</v>
+        <v>114571334</v>
       </c>
       <c r="B6" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1140,7 +1111,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1150,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581542</v>
+        <v>581410</v>
       </c>
       <c r="R6" t="n">
-        <v>6764691</v>
+        <v>6764652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,15 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114571336</v>
+        <v>114571335</v>
       </c>
       <c r="B7" t="n">
-        <v>91648</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581409</v>
+        <v>581406</v>
       </c>
       <c r="R7" t="n">
-        <v>6764646</v>
+        <v>6764645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,47 +1289,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114566558</v>
+        <v>114571336</v>
       </c>
       <c r="B8" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581647</v>
+        <v>581409</v>
       </c>
       <c r="R8" t="n">
-        <v>6764716</v>
+        <v>6764646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,49 +1383,49 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114571335</v>
+        <v>114566558</v>
       </c>
       <c r="B9" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4745</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581406</v>
+        <v>581647</v>
       </c>
       <c r="R9" t="n">
-        <v>6764645</v>
+        <v>6764716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1489,121 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114564946</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>581245</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6764659</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
